--- a/data/trans_camb/P38A-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P38A-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,19; -6,89</t>
+          <t>-19,06; -6,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 12,1</t>
+          <t>-0,3; 12,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 3,2</t>
+          <t>-8,53; 3,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 15,0</t>
+          <t>6,46; 14,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,36; -3,38</t>
+          <t>-12,25; -3,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 12,46</t>
+          <t>4,18; 12,02</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,79; -8,14</t>
+          <t>-21,75; -7,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 14,4</t>
+          <t>-0,32; 14,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 3,76</t>
+          <t>-9,33; 4,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 18,0</t>
+          <t>7,05; 17,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,84; -3,89</t>
+          <t>-13,78; -4,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 14,69</t>
+          <t>4,74; 14,1</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 4,59</t>
+          <t>-4,24; 4,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 4,96</t>
+          <t>-6,6; 5,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 4,07</t>
+          <t>-2,25; 3,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 2,35</t>
+          <t>-5,81; 1,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 3,28</t>
+          <t>-2,22; 3,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 2,25</t>
+          <t>-4,21; 2,36</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 5,45</t>
+          <t>-4,81; 5,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 5,83</t>
+          <t>-7,34; 5,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 4,51</t>
+          <t>-2,36; 4,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 2,57</t>
+          <t>-6,2; 1,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 3,74</t>
+          <t>-2,45; 3,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 2,53</t>
+          <t>-4,7; 2,67</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 5,99</t>
+          <t>-3,79; 6,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 9,51</t>
+          <t>-0,26; 9,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 4,58</t>
+          <t>-3,43; 4,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 8,4</t>
+          <t>1,46; 8,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,33</t>
+          <t>-1,83; 4,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 7,78</t>
+          <t>2,29; 8,05</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 6,99</t>
+          <t>-4,16; 7,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 11,2</t>
+          <t>-0,21; 10,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 5,12</t>
+          <t>-3,64; 4,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,47</t>
+          <t>1,55; 9,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,9</t>
+          <t>-1,99; 4,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 8,86</t>
+          <t>2,48; 9,15</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,94; 16,76</t>
+          <t>6,53; 16,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 15,21</t>
+          <t>-0,25; 15,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 8,27</t>
+          <t>0,13; 8,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 7,1</t>
+          <t>-42,2; 7,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,77; 11,86</t>
+          <t>4,63; 11,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 9,34</t>
+          <t>-25,02; 9,08</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,19; 21,73</t>
+          <t>7,8; 21,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,11; 19,66</t>
+          <t>0,04; 20,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 9,67</t>
+          <t>0,31; 9,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,74; 8,06</t>
+          <t>-46,75; 7,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,41; 14,45</t>
+          <t>5,32; 13,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 11,17</t>
+          <t>-29,41; 10,84</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,94; -1,88</t>
+          <t>-16,28; -1,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 3,44</t>
+          <t>-11,15; 3,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 0,87</t>
+          <t>-9,16; 1,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 0,28</t>
+          <t>-9,79; 0,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,24; -2,26</t>
+          <t>-11,22; -2,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 0,45</t>
+          <t>-9,09; 0,47</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,84; -2,2</t>
+          <t>-18,28; -1,62</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 4,14</t>
+          <t>-12,7; 4,01</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 0,83</t>
+          <t>-9,65; 1,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 0,12</t>
+          <t>-10,4; 0,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-12,28; -2,57</t>
+          <t>-12,13; -2,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 0,51</t>
+          <t>-9,9; 0,54</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,74; -0,71</t>
+          <t>-11,79; -0,6</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 8,14</t>
+          <t>-1,5; 8,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 0,95</t>
+          <t>-7,15; 0,95</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 5,3</t>
+          <t>-1,24; 5,52</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,18; -0,9</t>
+          <t>-8,17; -1,17</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 5,47</t>
+          <t>-0,17; 5,58</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-12,7; -0,82</t>
+          <t>-12,79; -0,69</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 9,21</t>
+          <t>-1,61; 9,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 1,03</t>
+          <t>-7,48; 0,99</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 5,66</t>
+          <t>-1,27; 5,93</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-8,77; -1,01</t>
+          <t>-8,66; -1,29</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 5,95</t>
+          <t>-0,18; 6,1</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-21,31; -12,81</t>
+          <t>-21,44; -12,62</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -1,55</t>
+          <t>-11,85; -1,48</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,09; -9,91</t>
+          <t>-17,07; -10,25</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 4,24</t>
+          <t>-3,5; 4,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-18,23; -12,77</t>
+          <t>-18,41; -12,43</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 2,0</t>
+          <t>-5,87; 1,73</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-23,49; -14,63</t>
+          <t>-23,84; -14,44</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,27; -1,75</t>
+          <t>-13,09; -1,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,17; -10,79</t>
+          <t>-18,13; -11,03</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 4,62</t>
+          <t>-3,74; 5,17</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,71; -14,0</t>
+          <t>-19,93; -13,76</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 2,21</t>
+          <t>-6,37; 1,89</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>6,23; 13,75</t>
+          <t>6,43; 13,92</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-58,21; -11,68</t>
+          <t>-59,11; -11,41</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>9,0; 15,25</t>
+          <t>9,49; 15,43</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-12,24; -4,09</t>
+          <t>-12,5; -4,02</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>9,07; 13,82</t>
+          <t>8,84; 13,74</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-42,18; -9,72</t>
+          <t>-43,75; -9,57</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,65; 17,99</t>
+          <t>7,88; 18,21</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-72,83; -14,77</t>
+          <t>-72,79; -14,65</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10,7; 19,24</t>
+          <t>11,19; 19,43</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-14,6; -5,05</t>
+          <t>-15,0; -5,03</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>11,06; 17,41</t>
+          <t>10,79; 17,44</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-53,27; -12,12</t>
+          <t>-54,72; -11,95</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,11</t>
+          <t>-3,55; 0,03</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-24,37; -0,99</t>
+          <t>-25,32; -1,13</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,6</t>
+          <t>-1,36; 1,65</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 1,06</t>
+          <t>-7,16; 1,1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,37</t>
+          <t>-1,83; 0,36</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-14,0; -0,63</t>
+          <t>-14,12; -0,77</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,14</t>
+          <t>-4,12; 0,03</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-28,58; -1,16</t>
+          <t>-29,6; -1,35</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,81</t>
+          <t>-1,5; 1,85</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 1,18</t>
+          <t>-7,99; 1,22</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,43</t>
+          <t>-2,08; 0,41</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-15,94; -0,73</t>
+          <t>-16,3; -0,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38A-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P38A-Provincia-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,4</t>
+          <t>8,48</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,47</t>
+          <t>10,27</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,35</t>
+          <t>9,37</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,06; -6,04</t>
+          <t>-19,69; -6,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 12,06</t>
+          <t>3,44; 13,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 3,5</t>
+          <t>-8,19; 3,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 14,9</t>
+          <t>6,08; 14,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,25; -3,66</t>
+          <t>-12,7; -3,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 12,02</t>
+          <t>6,18; 12,67</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,75; -7,28</t>
+          <t>-22,11; -7,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 14,31</t>
+          <t>3,81; 16,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 4,11</t>
+          <t>-9,01; 3,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 17,88</t>
+          <t>6,74; 17,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,78; -4,24</t>
+          <t>-14,24; -4,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 14,1</t>
+          <t>6,98; 14,88</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,55</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,35</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 4,62</t>
+          <t>-4,28; 4,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 5,07</t>
+          <t>-4,8; 5,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 3,93</t>
+          <t>-2,53; 3,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 1,69</t>
+          <t>-5,03; 2,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 3,25</t>
+          <t>-2,54; 3,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 2,36</t>
+          <t>-3,95; 2,57</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-0,25%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,68%</t>
+          <t>-1,36%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,06%</t>
+          <t>-0,39%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 5,49</t>
+          <t>-4,84; 5,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 5,93</t>
+          <t>-5,31; 6,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 4,38</t>
+          <t>-2,71; 4,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 1,87</t>
+          <t>-5,35; 2,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,69</t>
+          <t>-2,78; 3,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 2,67</t>
+          <t>-4,35; 2,89</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>4,62</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,89</t>
+          <t>4,6</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>4,67</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 6,13</t>
+          <t>-3,73; 5,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 9,11</t>
+          <t>-0,24; 9,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 4,37</t>
+          <t>-2,92; 4,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 8,32</t>
+          <t>1,54; 8,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 4,23</t>
+          <t>-1,92; 4,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,05</t>
+          <t>1,94; 7,66</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 7,17</t>
+          <t>-4,12; 6,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 10,68</t>
+          <t>-0,3; 10,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 4,88</t>
+          <t>-3,12; 5,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 9,26</t>
+          <t>1,64; 8,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,78</t>
+          <t>-2,08; 4,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,48; 9,15</t>
+          <t>2,11; 8,61</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9,37</t>
+          <t>7,09</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-8,03</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>5,92</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,53; 16,62</t>
+          <t>6,01; 16,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 15,88</t>
+          <t>-2,13; 13,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 8,13</t>
+          <t>0,03; 8,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 7,01</t>
+          <t>-0,15; 8,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,63; 11,38</t>
+          <t>4,8; 11,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 9,08</t>
+          <t>1,8; 9,81</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-9,05%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-0,42%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,8; 21,67</t>
+          <t>7,21; 22,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,04; 20,64</t>
+          <t>-2,29; 17,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 9,56</t>
+          <t>0,08; 9,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,75; 7,92</t>
+          <t>-0,15; 10,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,32; 13,88</t>
+          <t>5,58; 13,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 10,84</t>
+          <t>2,08; 11,91</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-3,66</t>
+          <t>-7,35</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-4,73</t>
+          <t>-6,4</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,02</t>
+          <t>-6,73</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,28; -1,29</t>
+          <t>-16,34; -1,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 3,43</t>
+          <t>-14,94; -0,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 1,62</t>
+          <t>-9,35; 0,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 0,14</t>
+          <t>-11,7; -1,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,22; -2,21</t>
+          <t>-11,04; -1,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 0,47</t>
+          <t>-11,24; -2,2</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-4,22%</t>
+          <t>-8,47%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-6,86%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-4,47%</t>
+          <t>-7,47%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -1,62</t>
+          <t>-18,1; -1,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 4,01</t>
+          <t>-16,72; -0,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 1,8</t>
+          <t>-9,81; 0,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 0,15</t>
+          <t>-12,37; -1,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-12,13; -2,47</t>
+          <t>-12,05; -2,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 0,54</t>
+          <t>-12,27; -2,56</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>1,98</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,65</t>
+          <t>1,97</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,79; -0,6</t>
+          <t>-11,6; -0,46</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 8,5</t>
+          <t>-2,2; 7,03</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 0,95</t>
+          <t>-7,29; 0,94</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 5,52</t>
+          <t>-1,66; 5,23</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,17; -1,17</t>
+          <t>-8,3; -1,31</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,58</t>
+          <t>-0,84; 4,88</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-12,79; -0,69</t>
+          <t>-12,55; -0,45</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 9,6</t>
+          <t>-2,36; 7,92</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 0,99</t>
+          <t>-7,57; 0,99</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 5,93</t>
+          <t>-1,69; 5,65</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-8,66; -1,29</t>
+          <t>-8,77; -1,43</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 6,1</t>
+          <t>-0,88; 5,34</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-6,23</t>
+          <t>-4,99</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-2,23</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,5</t>
+          <t>-3,54</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-21,44; -12,62</t>
+          <t>-21,67; -12,65</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,85; -1,48</t>
+          <t>-9,38; -0,53</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,07; -10,25</t>
+          <t>-16,98; -9,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 4,7</t>
+          <t>-4,96; 0,27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-18,41; -12,43</t>
+          <t>-18,1; -12,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 1,73</t>
+          <t>-6,11; -0,83</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-6,95%</t>
+          <t>-5,57%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-0,2%</t>
+          <t>-2,39%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-2,73%</t>
+          <t>-3,86%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-23,84; -14,44</t>
+          <t>-24,06; -14,33</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,09; -1,71</t>
+          <t>-10,33; -0,6</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,13; -11,03</t>
+          <t>-18,01; -10,71</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 5,17</t>
+          <t>-5,22; 0,34</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,93; -13,76</t>
+          <t>-19,75; -13,87</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 1,89</t>
+          <t>-6,6; -0,9</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-30,47</t>
+          <t>-15,08</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-8,19</t>
+          <t>-9,78</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-21,03</t>
+          <t>-12,39</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>6,43; 13,92</t>
+          <t>6,38; 14,02</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-59,11; -11,41</t>
+          <t>-19,47; -10,06</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>9,49; 15,43</t>
+          <t>9,46; 15,55</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-12,5; -4,02</t>
+          <t>-14,28; -5,62</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,74</t>
+          <t>8,88; 13,84</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-43,75; -9,57</t>
+          <t>-15,62; -9,39</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-38,79%</t>
+          <t>-19,2%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-9,99%</t>
+          <t>-11,92%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-26,18%</t>
+          <t>-15,42%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,88; 18,21</t>
+          <t>7,88; 18,4</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-72,79; -14,65</t>
+          <t>-24,44; -13,17</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11,19; 19,43</t>
+          <t>11,23; 19,47</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-15,0; -5,03</t>
+          <t>-17,13; -6,95</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>10,79; 17,44</t>
+          <t>10,82; 17,57</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-54,72; -11,95</t>
+          <t>-19,08; -11,89</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-7,66</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-1,43</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-4,44</t>
+          <t>-1,88</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,03</t>
+          <t>-3,52; -0,01</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-25,32; -1,13</t>
+          <t>-4,83; -0,7</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,65</t>
+          <t>-1,29; 1,63</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 1,1</t>
+          <t>-2,56; 0,49</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,36</t>
+          <t>-1,9; 0,34</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-14,12; -0,77</t>
+          <t>-3,13; -0,66</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-8,97%</t>
+          <t>-3,08%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-1,6%</t>
+          <t>-1,33%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-2,14%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 0,03</t>
+          <t>-4,07; -0,02</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-29,6; -1,35</t>
+          <t>-5,64; -0,84</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,85</t>
+          <t>-1,42; 1,82</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 1,22</t>
+          <t>-2,83; 0,55</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,41</t>
+          <t>-2,15; 0,39</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-16,3; -0,9</t>
+          <t>-3,56; -0,78</t>
         </is>
       </c>
     </row>
